--- a/cli/test_logging.xlsx
+++ b/cli/test_logging.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Glue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lambda" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ECS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Glue Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ECS Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,46 +438,6 @@
           <t>ExecutionId</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Lambda_TestCPU_cpu_total</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Lambda_TestCPU_mem_util</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Lambda_TestCPU_duration</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ECS_TestTask_Duration</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ECS_TestTask_CPU_MaxAvg</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ECS_TestTask_Mem_MaxAvg</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ECS_TestTask_CPU_TimeSeries</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ECS_TestTask_Mem_TimeSeries</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +445,49 @@
           <t>UNKNOWN</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ExecutionId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TestCPU_cpu_total</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TestCPU_mem_util</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TestCPU_duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="B2" t="n">
         <v>16</v>
       </c>
@@ -490,25 +497,229 @@
       <c r="D2" t="n">
         <v>1248</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ExecutionId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TestTask_Duration</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TestTask_CPU_MaxAvg</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TestTask_Mem_MaxAvg</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TestTask_CPU_Avg_TimeSeries</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TestTask_CPU_Max_TimeSeries</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TestTask_Mem_Avg_TimeSeries</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TestTask_Mem_Max_TimeSeries</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5.00, 10.50, 50.00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10.00, 20.00, 80.00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ExecutionId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ResourceName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StepName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Time_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mem_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Time_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mem_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Time_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mem_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TestTask</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-08T02:10:00+00:00</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-01-08T02:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-01-08T02:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>50</v>
       </c>
-      <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5.00/10.00, 10.50/20.00, 50.00/80.00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30.00/35.00</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
